--- a/EKG_Kalite_Yönetim_Sistemi/98_Uygulama_Kayıtları/04_Parça ve Proses Kontrolü/EKG-KLT-FRM-24_ece_r43_parcalanma_test_raporu__dolu_ornek.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/98_Uygulama_Kayıtları/04_Parça ve Proses Kontrolü/EKG-KLT-FRM-24_ece_r43_parcalanma_test_raporu__dolu_ornek.xlsx
@@ -1531,7 +1531,8 @@
   <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-24&amp;C&amp;"Arial,Regular"&amp;11ECE R43 Parçalanma Test Raporu - Dolu Örnek</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 28.09.2026
+Revizyon nedeni: Kaynak test verileri korundu; yöntem ve mevzuat doğrulaması gereğini açıklayan uyarı eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
